--- a/results/reliability_eval/reliability_eval_09-17-1-test/Llama-3-8B_P101_0_sample_25_tokens_0.1_temp_reflective_reasoning_scores_09-17-1-test.xlsx
+++ b/results/reliability_eval/reliability_eval_09-17-1-test/Llama-3-8B_P101_0_sample_25_tokens_0.1_temp_reflective_reasoning_scores_09-17-1-test.xlsx
@@ -516,14 +516,14 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>8.125674734534483</v>
+        <v>8.507114796420598</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.6058027088974338</v>
+        <v>0.6709596337604224</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
